--- a/data-manipulation-scripts/sheets-cleanup/sheets/CAIXA DIREÇÃO - 30_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/CAIXA DIREÇÃO - 30_01.xlsx
@@ -482,7 +482,9 @@
       <c r="C2" s="2">
         <v>1.0</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" s="2">
+        <v>35.0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1"/>
@@ -492,7 +494,9 @@
       <c r="C3" s="2">
         <v>1.0</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" s="2">
+        <v>35.0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
@@ -504,7 +508,9 @@
       <c r="C4" s="2">
         <v>5.0</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" s="2">
+        <v>35.0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3"/>
@@ -528,7 +534,9 @@
       <c r="C6" s="2">
         <v>4.0</v>
       </c>
-      <c r="D6" s="4"/>
+      <c r="D6" s="2">
+        <v>35.0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
@@ -540,7 +548,9 @@
       <c r="C7" s="2">
         <v>4.0</v>
       </c>
-      <c r="D7" s="4"/>
+      <c r="D7" s="2">
+        <v>35.0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
@@ -552,7 +562,9 @@
       <c r="C8" s="2">
         <v>4.0</v>
       </c>
-      <c r="D8" s="4"/>
+      <c r="D8" s="2">
+        <v>35.0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
@@ -564,7 +576,9 @@
       <c r="C9" s="2">
         <v>10.0</v>
       </c>
-      <c r="D9" s="4"/>
+      <c r="D9" s="2">
+        <v>35.0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
@@ -576,7 +590,9 @@
       <c r="C10" s="2">
         <v>9.0</v>
       </c>
-      <c r="D10" s="4"/>
+      <c r="D10" s="2">
+        <v>35.0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
@@ -588,7 +604,9 @@
       <c r="C11" s="2">
         <v>7.0</v>
       </c>
-      <c r="D11" s="4"/>
+      <c r="D11" s="2">
+        <v>35.0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
@@ -600,7 +618,9 @@
       <c r="C12" s="2">
         <v>2.0</v>
       </c>
-      <c r="D12" s="4"/>
+      <c r="D12" s="2">
+        <v>35.0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
@@ -612,7 +632,9 @@
       <c r="C13" s="2">
         <v>4.0</v>
       </c>
-      <c r="D13" s="4"/>
+      <c r="D13" s="2">
+        <v>35.0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
@@ -624,7 +646,9 @@
       <c r="C14" s="2">
         <v>3.0</v>
       </c>
-      <c r="D14" s="4"/>
+      <c r="D14" s="2">
+        <v>35.0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
@@ -636,7 +660,9 @@
       <c r="C15" s="2">
         <v>3.0</v>
       </c>
-      <c r="D15" s="4"/>
+      <c r="D15" s="2">
+        <v>35.0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
@@ -648,7 +674,9 @@
       <c r="C16" s="2">
         <v>1.0</v>
       </c>
-      <c r="D16" s="4"/>
+      <c r="D16" s="2">
+        <v>35.0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
@@ -660,7 +688,9 @@
       <c r="C17" s="2">
         <v>2.0</v>
       </c>
-      <c r="D17" s="4"/>
+      <c r="D17" s="2">
+        <v>35.0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
@@ -672,7 +702,9 @@
       <c r="C18" s="2">
         <v>11.0</v>
       </c>
-      <c r="D18" s="4"/>
+      <c r="D18" s="2">
+        <v>48.0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
@@ -684,7 +716,9 @@
       <c r="C19" s="2">
         <v>1.0</v>
       </c>
-      <c r="D19" s="4"/>
+      <c r="D19" s="2">
+        <v>35.0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
@@ -696,7 +730,9 @@
       <c r="C20" s="2">
         <v>1.0</v>
       </c>
-      <c r="D20" s="4"/>
+      <c r="D20" s="2">
+        <v>60.0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
@@ -708,7 +744,9 @@
       <c r="C21" s="2">
         <v>1.0</v>
       </c>
-      <c r="D21" s="4"/>
+      <c r="D21" s="2">
+        <v>55.0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
@@ -720,7 +758,9 @@
       <c r="C22" s="2">
         <v>1.0</v>
       </c>
-      <c r="D22" s="4"/>
+      <c r="D22" s="2">
+        <v>35.0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
@@ -732,7 +772,9 @@
       <c r="C23" s="2">
         <v>1.0</v>
       </c>
-      <c r="D23" s="4"/>
+      <c r="D23" s="2">
+        <v>45.0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
@@ -744,7 +786,9 @@
       <c r="C24" s="2">
         <v>4.0</v>
       </c>
-      <c r="D24" s="4"/>
+      <c r="D24" s="2">
+        <v>60.0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
@@ -770,7 +814,9 @@
       <c r="C26" s="2">
         <v>1.0</v>
       </c>
-      <c r="D26" s="4"/>
+      <c r="D26" s="2">
+        <v>40.0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
@@ -782,7 +828,9 @@
       <c r="C27" s="2">
         <v>1.0</v>
       </c>
-      <c r="D27" s="4"/>
+      <c r="D27" s="2">
+        <v>40.0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3"/>
@@ -804,7 +852,9 @@
       <c r="C29" s="2">
         <v>8.0</v>
       </c>
-      <c r="D29" s="4"/>
+      <c r="D29" s="2">
+        <v>80.0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="3"/>
